--- a/R_Codes/DataSummary/All_Prokaryotes/Sample_Type/All_Prokaryotes_Summary_Phylum_by_Sample_Type.xlsx
+++ b/R_Codes/DataSummary/All_Prokaryotes/Sample_Type/All_Prokaryotes_Summary_Phylum_by_Sample_Type.xlsx
@@ -609,10 +609,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>21.7609266136752</v>
+        <v>21.7622773575215</v>
       </c>
       <c r="D2" t="n">
-        <v>0.240627134478429</v>
+        <v>0.24065772968727</v>
       </c>
     </row>
     <row r="3">
@@ -623,10 +623,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>10.0832045034164</v>
+        <v>10.0835695604787</v>
       </c>
       <c r="D3" t="n">
-        <v>0.122239385124135</v>
+        <v>0.122638013213039</v>
       </c>
     </row>
     <row r="4">
@@ -637,10 +637,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>7.67074898905725</v>
+        <v>7.67035526264039</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0911385631254121</v>
+        <v>0.0911317981196219</v>
       </c>
     </row>
     <row r="5">
@@ -651,10 +651,10 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>6.91857086316109</v>
+        <v>6.91866081336333</v>
       </c>
       <c r="D5" t="n">
-        <v>0.124172617812163</v>
+        <v>0.124170619654835</v>
       </c>
     </row>
     <row r="6">
@@ -665,10 +665,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>5.78196952153187</v>
+        <v>5.78175384328398</v>
       </c>
       <c r="D6" t="n">
-        <v>0.173895046899155</v>
+        <v>0.173891851031029</v>
       </c>
     </row>
     <row r="7">
@@ -679,10 +679,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>4.78101842415757</v>
+        <v>4.78105021624774</v>
       </c>
       <c r="D7" t="n">
-        <v>0.260105197121463</v>
+        <v>0.260110951841298</v>
       </c>
     </row>
     <row r="8">
@@ -693,10 +693,10 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>4.75112364897646</v>
+        <v>4.75077424714615</v>
       </c>
       <c r="D8" t="n">
-        <v>0.129801582746227</v>
+        <v>0.129793138447533</v>
       </c>
     </row>
     <row r="9">
@@ -707,10 +707,10 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>4.31632550610984</v>
+        <v>4.31494152258331</v>
       </c>
       <c r="D9" t="n">
-        <v>0.725800213673338</v>
+        <v>0.725507562537395</v>
       </c>
     </row>
     <row r="10">
@@ -721,10 +721,10 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>3.28238491504789</v>
+        <v>3.28226886000876</v>
       </c>
       <c r="D10" t="n">
-        <v>0.106971006927844</v>
+        <v>0.106967135986772</v>
       </c>
     </row>
     <row r="11">
@@ -735,10 +735,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>3.02506808672434</v>
+        <v>3.02516408871599</v>
       </c>
       <c r="D11" t="n">
-        <v>0.233309854205774</v>
+        <v>0.233320384039409</v>
       </c>
     </row>
     <row r="12">
@@ -749,10 +749,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>2.96974705539577</v>
+        <v>2.97005297943848</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0686003398598993</v>
+        <v>0.0686106472512165</v>
       </c>
     </row>
     <row r="13">
@@ -763,10 +763,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>2.36803476006497</v>
+        <v>2.36796288589534</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0847669645851135</v>
+        <v>0.0847630239866693</v>
       </c>
     </row>
     <row r="14">
@@ -777,10 +777,10 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>2.26675503353507</v>
+        <v>2.26695125312262</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0418533205527473</v>
+        <v>0.0418574721223817</v>
       </c>
     </row>
     <row r="15">
@@ -791,10 +791,10 @@
         <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>2.16120215614226</v>
+        <v>2.16190915247882</v>
       </c>
       <c r="D15" t="n">
-        <v>0.630839632185262</v>
+        <v>0.631046876611651</v>
       </c>
     </row>
     <row r="16">
@@ -805,10 +805,10 @@
         <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>1.78431039450407</v>
+        <v>1.78449052469228</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0132479013162543</v>
+        <v>0.0132512817326122</v>
       </c>
     </row>
     <row r="17">
@@ -819,10 +819,10 @@
         <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>1.56894865858386</v>
+        <v>1.568986544644</v>
       </c>
       <c r="D17" t="n">
-        <v>0.158045752393243</v>
+        <v>0.158054034060133</v>
       </c>
     </row>
     <row r="18">
@@ -833,10 +833,10 @@
         <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>1.43192150213586</v>
+        <v>1.43198268437643</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0873671621098392</v>
+        <v>0.087374396443473</v>
       </c>
     </row>
     <row r="19">
@@ -847,10 +847,10 @@
         <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>1.30185458681485</v>
+        <v>1.30212288353511</v>
       </c>
       <c r="D19" t="n">
-        <v>0.12398872214353</v>
+        <v>0.124013734188933</v>
       </c>
     </row>
     <row r="20">
@@ -861,10 +861,10 @@
         <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>1.23583942632259</v>
+        <v>1.23597398972075</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0133493632071244</v>
+        <v>0.0133513804935949</v>
       </c>
     </row>
     <row r="21">
@@ -875,10 +875,10 @@
         <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>1.15782568183839</v>
+        <v>1.15781211665459</v>
       </c>
       <c r="D21" t="n">
-        <v>0.388147454124298</v>
+        <v>0.388147147303828</v>
       </c>
     </row>
     <row r="22">
@@ -889,10 +889,10 @@
         <v>25</v>
       </c>
       <c r="C22" t="n">
-        <v>0.914810625981458</v>
+        <v>0.914748471908951</v>
       </c>
       <c r="D22" t="n">
-        <v>0.112719322261636</v>
+        <v>0.112713526040406</v>
       </c>
     </row>
     <row r="23">
@@ -903,10 +903,10 @@
         <v>26</v>
       </c>
       <c r="C23" t="n">
-        <v>0.837110437409499</v>
+        <v>0.837026874985027</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0246533465768839</v>
+        <v>0.0246501059907574</v>
       </c>
     </row>
     <row r="24">
@@ -917,10 +917,10 @@
         <v>27</v>
       </c>
       <c r="C24" t="n">
-        <v>0.81902960218412</v>
+        <v>0.817827013939666</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0866843549646087</v>
+        <v>0.0910654503357963</v>
       </c>
     </row>
     <row r="25">
@@ -931,10 +931,10 @@
         <v>28</v>
       </c>
       <c r="C25" t="n">
-        <v>0.70854617892614</v>
+        <v>0.708597430077996</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0723915203508276</v>
+        <v>0.0723993903413844</v>
       </c>
     </row>
     <row r="26">
@@ -945,10 +945,10 @@
         <v>29</v>
       </c>
       <c r="C26" t="n">
-        <v>0.660269625967694</v>
+        <v>0.660353895473854</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0185273727082479</v>
+        <v>0.0185283817921405</v>
       </c>
     </row>
     <row r="27">
@@ -959,10 +959,10 @@
         <v>30</v>
       </c>
       <c r="C27" t="n">
-        <v>0.630804205125401</v>
+        <v>0.630698100890269</v>
       </c>
       <c r="D27" t="n">
-        <v>0.21514285032078</v>
+        <v>0.215099761008479</v>
       </c>
     </row>
     <row r="28">
@@ -973,10 +973,10 @@
         <v>31</v>
       </c>
       <c r="C28" t="n">
-        <v>0.406629786645901</v>
+        <v>0.406617206121492</v>
       </c>
       <c r="D28" t="n">
-        <v>0.17598432539977</v>
+        <v>0.175977369525517</v>
       </c>
     </row>
     <row r="29">
@@ -987,10 +987,10 @@
         <v>32</v>
       </c>
       <c r="C29" t="n">
-        <v>0.376478799111195</v>
+        <v>0.376460428719311</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0569277071811371</v>
+        <v>0.0569255066041069</v>
       </c>
     </row>
     <row r="30">
@@ -1001,10 +1001,10 @@
         <v>33</v>
       </c>
       <c r="C30" t="n">
-        <v>0.319907100323329</v>
+        <v>0.319966284722752</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0792373807900135</v>
+        <v>0.0792516795713162</v>
       </c>
     </row>
     <row r="31">
@@ -1015,10 +1015,10 @@
         <v>34</v>
       </c>
       <c r="C31" t="n">
-        <v>0.311547220728577</v>
+        <v>0.311533277594606</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0172972008546067</v>
+        <v>0.017295263988654</v>
       </c>
     </row>
     <row r="32">
@@ -1029,10 +1029,10 @@
         <v>35</v>
       </c>
       <c r="C32" t="n">
-        <v>0.303531346920234</v>
+        <v>0.303578981210747</v>
       </c>
       <c r="D32" t="n">
-        <v>0.017466941321902</v>
+        <v>0.0174706884831037</v>
       </c>
     </row>
     <row r="33">
@@ -1043,10 +1043,10 @@
         <v>36</v>
       </c>
       <c r="C33" t="n">
-        <v>0.276621159496425</v>
+        <v>0.276639768738065</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0136147728685635</v>
+        <v>0.0136172519351224</v>
       </c>
     </row>
     <row r="34">
@@ -1057,10 +1057,10 @@
         <v>37</v>
       </c>
       <c r="C34" t="n">
-        <v>0.257536867560212</v>
+        <v>0.257546713674983</v>
       </c>
       <c r="D34" t="n">
-        <v>0.00630636905983868</v>
+        <v>0.00630700331476103</v>
       </c>
     </row>
     <row r="35">
@@ -1071,10 +1071,10 @@
         <v>38</v>
       </c>
       <c r="C35" t="n">
-        <v>0.240955188548261</v>
+        <v>0.240932634902632</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0196478778738606</v>
+        <v>0.019645659674528</v>
       </c>
     </row>
     <row r="36">
@@ -1085,10 +1085,10 @@
         <v>39</v>
       </c>
       <c r="C36" t="n">
-        <v>0.230585283865868</v>
+        <v>0.230564123421666</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0509844526870072</v>
+        <v>0.0509783767753283</v>
       </c>
     </row>
     <row r="37">
@@ -1099,10 +1099,10 @@
         <v>40</v>
       </c>
       <c r="C37" t="n">
-        <v>0.219742906044752</v>
+        <v>0.21975122573986</v>
       </c>
       <c r="D37" t="n">
-        <v>0.00600844586702114</v>
+        <v>0.0060086872243454</v>
       </c>
     </row>
     <row r="38">
@@ -1113,10 +1113,10 @@
         <v>41</v>
       </c>
       <c r="C38" t="n">
-        <v>0.199526690045392</v>
+        <v>0.199526182780347</v>
       </c>
       <c r="D38" t="n">
-        <v>0.00331135266480902</v>
+        <v>0.00331114598644298</v>
       </c>
     </row>
     <row r="39">
@@ -1127,10 +1127,10 @@
         <v>42</v>
       </c>
       <c r="C39" t="n">
-        <v>0.180419394007164</v>
+        <v>0.18040569029904</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0166865917056073</v>
+        <v>0.0166850776816214</v>
       </c>
     </row>
     <row r="40">
@@ -1141,10 +1141,10 @@
         <v>43</v>
       </c>
       <c r="C40" t="n">
-        <v>0.175302426010932</v>
+        <v>0.175282668877571</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0704758478739547</v>
+        <v>0.0704671562035202</v>
       </c>
     </row>
     <row r="41">
@@ -1155,10 +1155,10 @@
         <v>44</v>
       </c>
       <c r="C41" t="n">
-        <v>0.169975364996057</v>
+        <v>0.169955366435392</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0222827397611038</v>
+        <v>0.0222798777174903</v>
       </c>
     </row>
     <row r="42">
@@ -1169,10 +1169,10 @@
         <v>45</v>
       </c>
       <c r="C42" t="n">
-        <v>0.158651012341907</v>
+        <v>0.158673366659809</v>
       </c>
       <c r="D42" t="n">
-        <v>0.045737570407468</v>
+        <v>0.0457539772131932</v>
       </c>
     </row>
     <row r="43">
@@ -1183,10 +1183,10 @@
         <v>46</v>
       </c>
       <c r="C43" t="n">
-        <v>0.137410891541032</v>
+        <v>0.137395260037261</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0449355261351212</v>
+        <v>0.0449289816918205</v>
       </c>
     </row>
     <row r="44">
@@ -1197,10 +1197,10 @@
         <v>47</v>
       </c>
       <c r="C44" t="n">
-        <v>0.137143232701889</v>
+        <v>0.137167318408933</v>
       </c>
       <c r="D44" t="n">
-        <v>0.00308459967368937</v>
+        <v>0.00308513793538259</v>
       </c>
     </row>
     <row r="45">
@@ -1211,10 +1211,10 @@
         <v>48</v>
       </c>
       <c r="C45" t="n">
-        <v>0.08329335259299</v>
+        <v>0.0832918371541882</v>
       </c>
       <c r="D45" t="n">
-        <v>0.00412519462388737</v>
+        <v>0.00412483158417483</v>
       </c>
     </row>
     <row r="46">
@@ -1225,10 +1225,10 @@
         <v>49</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0692411801897809</v>
+        <v>0.0692410464152097</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0243421446622777</v>
+        <v>0.0243414152156006</v>
       </c>
     </row>
     <row r="47">
@@ -1239,10 +1239,10 @@
         <v>50</v>
       </c>
       <c r="C47" t="n">
-        <v>0.067218041652683</v>
+        <v>0.0672108440905825</v>
       </c>
       <c r="D47" t="n">
-        <v>0.00668684478327204</v>
+        <v>0.00668616124790953</v>
       </c>
     </row>
     <row r="48">
@@ -1253,7 +1253,7 @@
         <v>51</v>
       </c>
       <c r="C48" t="n">
-        <v>0.06156481136528</v>
+        <v>0.0615545147950379</v>
       </c>
       <c r="D48"/>
     </row>
@@ -1265,10 +1265,10 @@
         <v>52</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0558564601377837</v>
+        <v>0.0558554742148481</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0072784081124607</v>
+        <v>0.00727819198305638</v>
       </c>
     </row>
     <row r="50">
@@ -1279,10 +1279,10 @@
         <v>53</v>
       </c>
       <c r="C50" t="n">
-        <v>0.041275304519162</v>
+        <v>0.0412794290949981</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0080909810456354</v>
+        <v>0.00809159300126105</v>
       </c>
     </row>
     <row r="51">
@@ -1293,10 +1293,10 @@
         <v>54</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0357424290263582</v>
+        <v>0.0357480677974404</v>
       </c>
       <c r="D51" t="n">
-        <v>0.00168638120545988</v>
+        <v>0.00168680940639728</v>
       </c>
     </row>
     <row r="52">
@@ -1307,10 +1307,10 @@
         <v>55</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0329751577979992</v>
+        <v>0.0329700569728601</v>
       </c>
       <c r="D52" t="n">
-        <v>0.00303624128538705</v>
+        <v>0.00303563958218496</v>
       </c>
     </row>
     <row r="53">
@@ -1321,10 +1321,10 @@
         <v>56</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0326582679579259</v>
+        <v>0.0326619136604909</v>
       </c>
       <c r="D53" t="n">
-        <v>0.00209412826448036</v>
+        <v>0.00209457650402667</v>
       </c>
     </row>
     <row r="54">
@@ -1335,7 +1335,7 @@
         <v>57</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0316309736631204</v>
+        <v>0.0316297890797849</v>
       </c>
       <c r="D54"/>
     </row>
@@ -1347,10 +1347,10 @@
         <v>58</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0313758170533332</v>
+        <v>0.0313841297664091</v>
       </c>
       <c r="D55" t="n">
-        <v>0.00523947935992204</v>
+        <v>0.00524152469478577</v>
       </c>
     </row>
     <row r="56">
@@ -1361,10 +1361,10 @@
         <v>59</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0298202618941446</v>
+        <v>0.0298250290235258</v>
       </c>
       <c r="D56" t="n">
-        <v>0.00668946759658577</v>
+        <v>0.00669114910307872</v>
       </c>
     </row>
     <row r="57">
@@ -1375,10 +1375,10 @@
         <v>60</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0295457685029536</v>
+        <v>0.0295461004520193</v>
       </c>
       <c r="D57" t="n">
-        <v>0.00598291523636964</v>
+        <v>0.00598137732196592</v>
       </c>
     </row>
     <row r="58">
@@ -1389,10 +1389,10 @@
         <v>61</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0256615203212098</v>
+        <v>0.0256641501038899</v>
       </c>
       <c r="D58" t="n">
-        <v>0.00664478539283624</v>
+        <v>0.00664577834495545</v>
       </c>
     </row>
     <row r="59">
@@ -1403,10 +1403,10 @@
         <v>62</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0178994139860595</v>
+        <v>0.0179009714449529</v>
       </c>
       <c r="D59" t="n">
-        <v>0.00235547475936501</v>
+        <v>0.00235512932184248</v>
       </c>
     </row>
     <row r="60">
@@ -1417,10 +1417,10 @@
         <v>63</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0140552285037183</v>
+        <v>0.0140572890748737</v>
       </c>
       <c r="D60" t="n">
-        <v>0.00201327935472589</v>
+        <v>0.0020135781075336</v>
       </c>
     </row>
     <row r="61">
@@ -1431,10 +1431,10 @@
         <v>64</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0114864371120666</v>
+        <v>0.0114842257669918</v>
       </c>
       <c r="D61" t="n">
-        <v>0.00438291868901427</v>
+        <v>0.00438250764268453</v>
       </c>
     </row>
     <row r="62">
@@ -1445,10 +1445,10 @@
         <v>65</v>
       </c>
       <c r="C62" t="n">
-        <v>0.00764347406992903</v>
+        <v>0.00764209855422093</v>
       </c>
       <c r="D62" t="n">
-        <v>0.00492737014416636</v>
+        <v>0.00492660482862357</v>
       </c>
     </row>
     <row r="63">
@@ -1459,7 +1459,7 @@
         <v>66</v>
       </c>
       <c r="C63" t="n">
-        <v>0.00654644511804976</v>
+        <v>0.00654815647051074</v>
       </c>
       <c r="D63"/>
     </row>
@@ -1471,7 +1471,7 @@
         <v>67</v>
       </c>
       <c r="C64" t="n">
-        <v>0.00591344335439638</v>
+        <v>0.00591442986738659</v>
       </c>
       <c r="D64"/>
     </row>
@@ -1483,10 +1483,10 @@
         <v>68</v>
       </c>
       <c r="C65" t="n">
-        <v>0.00558355119579296</v>
+        <v>0.00558395893937707</v>
       </c>
       <c r="D65" t="n">
-        <v>0.00115410349329897</v>
+        <v>0.00115438021349579</v>
       </c>
     </row>
     <row r="66">
@@ -1497,7 +1497,7 @@
         <v>69</v>
       </c>
       <c r="C66" t="n">
-        <v>0.00543441349094345</v>
+        <v>0.00543327530447121</v>
       </c>
       <c r="D66"/>
     </row>
@@ -1509,7 +1509,7 @@
         <v>70</v>
       </c>
       <c r="C67" t="n">
-        <v>0.00227296086236</v>
+        <v>0.00227236253405944</v>
       </c>
       <c r="D67"/>
     </row>
@@ -1521,7 +1521,7 @@
         <v>71</v>
       </c>
       <c r="C68" t="n">
-        <v>0.00131995759266029</v>
+        <v>0.00131999530673519</v>
       </c>
       <c r="D68"/>
     </row>
@@ -1533,10 +1533,10 @@
         <v>72</v>
       </c>
       <c r="C69" t="n">
-        <v>0.00128045054789576</v>
+        <v>0.00128144962202281</v>
       </c>
       <c r="D69" t="n">
-        <v>0.000133274109538564</v>
+        <v>0.00013329477761492</v>
       </c>
     </row>
     <row r="70">
@@ -1547,7 +1547,7 @@
         <v>73</v>
       </c>
       <c r="C70" t="n">
-        <v>0.00123255311809684</v>
+        <v>0.00123373961745808</v>
       </c>
       <c r="D70"/>
     </row>
@@ -1559,7 +1559,7 @@
         <v>74</v>
       </c>
       <c r="C71" t="n">
-        <v>0.000820479638527545</v>
+        <v>0.000820123314788007</v>
       </c>
       <c r="D71"/>
     </row>
@@ -1571,7 +1571,7 @@
         <v>75</v>
       </c>
       <c r="C72" t="n">
-        <v>0.00033617105601325</v>
+        <v>0.000336469391912891</v>
       </c>
       <c r="D72"/>
     </row>
@@ -1608,10 +1608,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>18.382148800274</v>
+        <v>18.5333276901263</v>
       </c>
       <c r="D2" t="n">
-        <v>0.198416131412961</v>
+        <v>0.200601749690914</v>
       </c>
     </row>
     <row r="3">
@@ -1622,10 +1622,10 @@
         <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>12.0999696818842</v>
+        <v>12.2942550378447</v>
       </c>
       <c r="D3" t="n">
-        <v>2.23517159324494</v>
+        <v>2.27260038332525</v>
       </c>
     </row>
     <row r="4">
@@ -1636,10 +1636,10 @@
         <v>21</v>
       </c>
       <c r="C4" t="n">
-        <v>9.37904063323832</v>
+        <v>9.51826180982964</v>
       </c>
       <c r="D4" t="n">
-        <v>1.30466364369722</v>
+        <v>1.32457755719025</v>
       </c>
     </row>
     <row r="5">
@@ -1647,13 +1647,13 @@
         <v>76</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>7.29857903009211</v>
+        <v>7.07882453649163</v>
       </c>
       <c r="D5" t="n">
-        <v>0.48956399296486</v>
+        <v>0.0646934065671636</v>
       </c>
     </row>
     <row r="6">
@@ -1661,13 +1661,13 @@
         <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>7.03050427790532</v>
+        <v>7.02613892299157</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0641151768668328</v>
+        <v>0.465930570105285</v>
       </c>
     </row>
     <row r="7">
@@ -1678,10 +1678,10 @@
         <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>6.43457936383208</v>
+        <v>6.4990922487162</v>
       </c>
       <c r="D7" t="n">
-        <v>0.518854068435167</v>
+        <v>0.523843098151598</v>
       </c>
     </row>
     <row r="8">
@@ -1692,10 +1692,10 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>6.35208268241865</v>
+        <v>6.40119867808807</v>
       </c>
       <c r="D8" t="n">
-        <v>0.129161436189485</v>
+        <v>0.13024037013382</v>
       </c>
     </row>
     <row r="9">
@@ -1706,10 +1706,10 @@
         <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>5.4651798959802</v>
+        <v>5.52137576482314</v>
       </c>
       <c r="D9" t="n">
-        <v>0.052656145120887</v>
+        <v>0.0531860801714665</v>
       </c>
     </row>
     <row r="10">
@@ -1720,10 +1720,10 @@
         <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>3.56762833346748</v>
+        <v>3.60183314118872</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0779809671398668</v>
+        <v>0.0787157120239988</v>
       </c>
     </row>
     <row r="11">
@@ -1731,13 +1731,13 @@
         <v>76</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>2.92029788776706</v>
+        <v>2.51656403844498</v>
       </c>
       <c r="D11" t="n">
-        <v>0.234683901899791</v>
+        <v>0.0487515974431266</v>
       </c>
     </row>
     <row r="12">
@@ -1745,13 +1745,13 @@
         <v>76</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>2.49184784743057</v>
+        <v>2.30819782560081</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0482833390030719</v>
+        <v>0.226907694182517</v>
       </c>
     </row>
     <row r="13">
@@ -1762,10 +1762,10 @@
         <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>2.08896295214265</v>
+        <v>2.10976773758954</v>
       </c>
       <c r="D13" t="n">
-        <v>0.025203593710464</v>
+        <v>0.0254703889469842</v>
       </c>
     </row>
     <row r="14">
@@ -1776,10 +1776,10 @@
         <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>2.03168782538129</v>
+        <v>2.05420942126975</v>
       </c>
       <c r="D14" t="n">
-        <v>0.219085653860976</v>
+        <v>0.221606781766431</v>
       </c>
     </row>
     <row r="15">
@@ -1790,10 +1790,10 @@
         <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>1.81310350205762</v>
+        <v>1.82672177958022</v>
       </c>
       <c r="D15" t="n">
-        <v>0.127449066855444</v>
+        <v>0.128645985832315</v>
       </c>
     </row>
     <row r="16">
@@ -1804,10 +1804,10 @@
         <v>48</v>
       </c>
       <c r="C16" t="n">
-        <v>1.73773970211574</v>
+        <v>1.73788672622751</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0972038291912338</v>
+        <v>0.0974928026959166</v>
       </c>
     </row>
     <row r="17">
@@ -1818,10 +1818,10 @@
         <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>1.28514251661013</v>
+        <v>1.28677439767439</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0280538192757856</v>
+        <v>0.0281743852971031</v>
       </c>
     </row>
     <row r="18">
@@ -1832,10 +1832,10 @@
         <v>36</v>
       </c>
       <c r="C18" t="n">
-        <v>1.2628840065347</v>
+        <v>1.27525830986112</v>
       </c>
       <c r="D18" t="n">
-        <v>0.04165915494304</v>
+        <v>0.0420629690718423</v>
       </c>
     </row>
     <row r="19">
@@ -1846,10 +1846,10 @@
         <v>28</v>
       </c>
       <c r="C19" t="n">
-        <v>1.02950143077532</v>
+        <v>1.03830527950649</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0606039317958023</v>
+        <v>0.0611987261765928</v>
       </c>
     </row>
     <row r="20">
@@ -1860,10 +1860,10 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>0.835467851231246</v>
+        <v>0.843785264834105</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0135068681137793</v>
+        <v>0.0136366010387442</v>
       </c>
     </row>
     <row r="21">
@@ -1874,10 +1874,10 @@
         <v>35</v>
       </c>
       <c r="C21" t="n">
-        <v>0.79557213080982</v>
+        <v>0.803336569337321</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0475960372654989</v>
+        <v>0.0480381674791535</v>
       </c>
     </row>
     <row r="22">
@@ -1888,10 +1888,10 @@
         <v>20</v>
       </c>
       <c r="C22" t="n">
-        <v>0.728939303586104</v>
+        <v>0.727231303959288</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08533384099916</v>
+        <v>0.0844364310389346</v>
       </c>
     </row>
     <row r="23">
@@ -1902,10 +1902,10 @@
         <v>11</v>
       </c>
       <c r="C23" t="n">
-        <v>0.53231820900024</v>
+        <v>0.537452727145315</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0128969765074405</v>
+        <v>0.0130265086890308</v>
       </c>
     </row>
     <row r="24">
@@ -1916,10 +1916,10 @@
         <v>33</v>
       </c>
       <c r="C24" t="n">
-        <v>0.433138109768814</v>
+        <v>0.437249810629596</v>
       </c>
       <c r="D24" t="n">
-        <v>0.170918567060812</v>
+        <v>0.172544225154919</v>
       </c>
     </row>
     <row r="25">
@@ -1930,10 +1930,10 @@
         <v>41</v>
       </c>
       <c r="C25" t="n">
-        <v>0.425997021095286</v>
+        <v>0.421058394543708</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0194991060086825</v>
+        <v>0.0188734343818287</v>
       </c>
     </row>
     <row r="26">
@@ -1944,10 +1944,10 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>0.37088930739431</v>
+        <v>0.374891186203305</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0596733269801258</v>
+        <v>0.0603501710173934</v>
       </c>
     </row>
     <row r="27">
@@ -1958,10 +1958,10 @@
         <v>54</v>
       </c>
       <c r="C27" t="n">
-        <v>0.322559052162815</v>
+        <v>0.325872129306395</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0110423899584782</v>
+        <v>0.0111491770541813</v>
       </c>
     </row>
     <row r="28">
@@ -1972,10 +1972,10 @@
         <v>23</v>
       </c>
       <c r="C28" t="n">
-        <v>0.318391951001908</v>
+        <v>0.317678042567438</v>
       </c>
       <c r="D28" t="n">
-        <v>0.00681613064820826</v>
+        <v>0.00674381513038208</v>
       </c>
     </row>
     <row r="29">
@@ -1986,10 +1986,10 @@
         <v>46</v>
       </c>
       <c r="C29" t="n">
-        <v>0.311623189052691</v>
+        <v>0.314669483987686</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0220995333354377</v>
+        <v>0.0223099636957097</v>
       </c>
     </row>
     <row r="30">
@@ -2000,10 +2000,10 @@
         <v>13</v>
       </c>
       <c r="C30" t="n">
-        <v>0.305811066574169</v>
+        <v>0.308986775826359</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0122885205500578</v>
+        <v>0.0124130913711245</v>
       </c>
     </row>
     <row r="31">
@@ -2014,10 +2014,10 @@
         <v>40</v>
       </c>
       <c r="C31" t="n">
-        <v>0.213153446507115</v>
+        <v>0.215393044492356</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0123975404435767</v>
+        <v>0.0125185883348391</v>
       </c>
     </row>
     <row r="32">
@@ -2028,10 +2028,10 @@
         <v>51</v>
       </c>
       <c r="C32" t="n">
-        <v>0.193949528009353</v>
+        <v>0.195970272665752</v>
       </c>
       <c r="D32" t="n">
-        <v>0.106489376473915</v>
+        <v>0.107557432972455</v>
       </c>
     </row>
     <row r="33">
@@ -2042,10 +2042,10 @@
         <v>47</v>
       </c>
       <c r="C33" t="n">
-        <v>0.15821557073128</v>
+        <v>0.160015008676312</v>
       </c>
       <c r="D33" t="n">
-        <v>0.00519667552375511</v>
+        <v>0.00526373805475789</v>
       </c>
     </row>
     <row r="34">
@@ -2056,10 +2056,10 @@
         <v>34</v>
       </c>
       <c r="C34" t="n">
-        <v>0.156631291605068</v>
+        <v>0.155081482625821</v>
       </c>
       <c r="D34" t="n">
-        <v>0.00988841897842502</v>
+        <v>0.00957300588467285</v>
       </c>
     </row>
     <row r="35">
@@ -2070,10 +2070,10 @@
         <v>43</v>
       </c>
       <c r="C35" t="n">
-        <v>0.107639211163976</v>
+        <v>0.108794356659839</v>
       </c>
       <c r="D35" t="n">
-        <v>0.028744368517691</v>
+        <v>0.0290445478347597</v>
       </c>
     </row>
     <row r="36">
@@ -2084,10 +2084,10 @@
         <v>18</v>
       </c>
       <c r="C36" t="n">
-        <v>0.101126518365119</v>
+        <v>0.102106311384776</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0157067411332251</v>
+        <v>0.0158547105903662</v>
       </c>
     </row>
     <row r="37">
@@ -2098,10 +2098,10 @@
         <v>42</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0987132006294671</v>
+        <v>0.099773327672455</v>
       </c>
       <c r="D37" t="n">
-        <v>0.00622806908915873</v>
+        <v>0.00629639076465932</v>
       </c>
     </row>
     <row r="38">
@@ -2112,10 +2112,10 @@
         <v>24</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0890420250863173</v>
+        <v>0.09001137746645</v>
       </c>
       <c r="D38" t="n">
-        <v>0.019072714477922</v>
+        <v>0.019300954403762</v>
       </c>
     </row>
     <row r="39">
@@ -2126,10 +2126,10 @@
         <v>65</v>
       </c>
       <c r="C39" t="n">
-        <v>0.079910122766446</v>
+        <v>0.0808196308559792</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0447853982793154</v>
+        <v>0.0452965340806616</v>
       </c>
     </row>
     <row r="40">
@@ -2140,10 +2140,10 @@
         <v>67</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0786202353082748</v>
+        <v>0.0795922373678087</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0348025089453629</v>
+        <v>0.0352438227503994</v>
       </c>
     </row>
     <row r="41">
@@ -2154,10 +2154,10 @@
         <v>37</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0758282964359459</v>
+        <v>0.0762795297972343</v>
       </c>
       <c r="D41" t="n">
-        <v>0.00179354153556445</v>
+        <v>0.00179389654034583</v>
       </c>
     </row>
     <row r="42">
@@ -2168,10 +2168,10 @@
         <v>56</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0711195866690807</v>
+        <v>0.0696937804075641</v>
       </c>
       <c r="D42" t="n">
-        <v>0.00656720286960041</v>
+        <v>0.00619216063132812</v>
       </c>
     </row>
     <row r="43">
@@ -2182,7 +2182,7 @@
         <v>77</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0616720518196562</v>
+        <v>0.0622869477174784</v>
       </c>
       <c r="D43"/>
     </row>
@@ -2194,10 +2194,10 @@
         <v>26</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0507192627455421</v>
+        <v>0.0507570992332053</v>
       </c>
       <c r="D44" t="n">
-        <v>0.00228967782609133</v>
+        <v>0.00226632631395943</v>
       </c>
     </row>
     <row r="45">
@@ -2208,10 +2208,10 @@
         <v>30</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0469127446703312</v>
+        <v>0.0473806391248837</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0151960570885899</v>
+        <v>0.0153517835288353</v>
       </c>
     </row>
     <row r="46">
@@ -2219,13 +2219,13 @@
         <v>76</v>
       </c>
       <c r="B46" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0437813523651193</v>
+        <v>0.0432826304881083</v>
       </c>
       <c r="D46" t="n">
-        <v>0.00795095344513261</v>
+        <v>0.0140210130386968</v>
       </c>
     </row>
     <row r="47">
@@ -2233,13 +2233,13 @@
         <v>76</v>
       </c>
       <c r="B47" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0428041170433677</v>
+        <v>0.0423879399442869</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0138642850309527</v>
+        <v>0.00746650017863547</v>
       </c>
     </row>
     <row r="48">
@@ -2250,10 +2250,10 @@
         <v>61</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0421616199056605</v>
+        <v>0.0412834945720465</v>
       </c>
       <c r="D48" t="n">
-        <v>0.00521934614397157</v>
+        <v>0.00497579739092518</v>
       </c>
     </row>
     <row r="49">
@@ -2264,10 +2264,10 @@
         <v>62</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0308869483731085</v>
+        <v>0.0311903454428294</v>
       </c>
       <c r="D49" t="n">
-        <v>0.00415267304237246</v>
+        <v>0.00419345281281257</v>
       </c>
     </row>
     <row r="50">
@@ -2278,10 +2278,10 @@
         <v>50</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0289131496577158</v>
+        <v>0.0292124903034522</v>
       </c>
       <c r="D50" t="n">
-        <v>0.00360430450124728</v>
+        <v>0.00364014967202993</v>
       </c>
     </row>
     <row r="51">
@@ -2292,10 +2292,10 @@
         <v>45</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0270327884912382</v>
+        <v>0.0272895431596136</v>
       </c>
       <c r="D51" t="n">
-        <v>0.00563254898061451</v>
+        <v>0.00568488609869415</v>
       </c>
     </row>
     <row r="52">
@@ -2306,10 +2306,10 @@
         <v>44</v>
       </c>
       <c r="C52" t="n">
-        <v>0.020339559490395</v>
+        <v>0.020570205265671</v>
       </c>
       <c r="D52" t="n">
-        <v>0.00267023546711689</v>
+        <v>0.00270189861788245</v>
       </c>
     </row>
     <row r="53">
@@ -2320,10 +2320,10 @@
         <v>31</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0201036858397776</v>
+        <v>0.0203050934801799</v>
       </c>
       <c r="D53" t="n">
-        <v>0.00699142257046306</v>
+        <v>0.00705913689371762</v>
       </c>
     </row>
     <row r="54">
@@ -2334,10 +2334,10 @@
         <v>60</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0160346707514044</v>
+        <v>0.0162144927087062</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0027184541110315</v>
+        <v>0.00275227989531451</v>
       </c>
     </row>
     <row r="55">
@@ -2348,10 +2348,10 @@
         <v>59</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0132314108335153</v>
+        <v>0.0133690643021268</v>
       </c>
       <c r="D55" t="n">
-        <v>0.0063332990493948</v>
+        <v>0.00639011660638637</v>
       </c>
     </row>
     <row r="56">
@@ -2362,10 +2362,10 @@
         <v>57</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0109911560752753</v>
+        <v>0.0111097776255183</v>
       </c>
       <c r="D56" t="n">
-        <v>0.0038344064565906</v>
+        <v>0.0038724545052133</v>
       </c>
     </row>
     <row r="57">
@@ -2376,10 +2376,10 @@
         <v>49</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0109140439633761</v>
+        <v>0.0110308277398645</v>
       </c>
       <c r="D57" t="n">
-        <v>0.00160511214397644</v>
+        <v>0.00162226739298024</v>
       </c>
     </row>
     <row r="58">
@@ -2390,10 +2390,10 @@
         <v>69</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0102790645337226</v>
+        <v>0.0103933697066224</v>
       </c>
       <c r="D58" t="n">
-        <v>0.00023156854493671</v>
+        <v>0.000223780193696136</v>
       </c>
     </row>
     <row r="59">
@@ -2404,10 +2404,10 @@
         <v>52</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0095866569318961</v>
+        <v>0.00968295542419775</v>
       </c>
       <c r="D59" t="n">
-        <v>0.00108480281586065</v>
+        <v>0.00109529121465298</v>
       </c>
     </row>
     <row r="60">
@@ -2418,10 +2418,10 @@
         <v>38</v>
       </c>
       <c r="C60" t="n">
-        <v>0.006937888138683</v>
+        <v>0.00701747080021754</v>
       </c>
       <c r="D60" t="n">
-        <v>0.00130603710284864</v>
+        <v>0.00132051999106952</v>
       </c>
     </row>
     <row r="61">
@@ -2432,10 +2432,10 @@
         <v>32</v>
       </c>
       <c r="C61" t="n">
-        <v>0.00642572759622504</v>
+        <v>0.00649425102915698</v>
       </c>
       <c r="D61" t="n">
-        <v>0.000926806877616954</v>
+        <v>0.00093680513191265</v>
       </c>
     </row>
     <row r="62">
@@ -2446,7 +2446,7 @@
         <v>78</v>
       </c>
       <c r="C62" t="n">
-        <v>0.00532000174362787</v>
+        <v>0.00538378957236859</v>
       </c>
       <c r="D62"/>
     </row>
@@ -2458,10 +2458,10 @@
         <v>64</v>
       </c>
       <c r="C63" t="n">
-        <v>0.00510403445013472</v>
+        <v>0.00516083527486673</v>
       </c>
       <c r="D63" t="n">
-        <v>0.000147521933680138</v>
+        <v>0.000150430195464483</v>
       </c>
     </row>
     <row r="64">
@@ -2472,10 +2472,10 @@
         <v>53</v>
       </c>
       <c r="C64" t="n">
-        <v>0.00238560452785668</v>
+        <v>0.002408790867241</v>
       </c>
       <c r="D64" t="n">
-        <v>0.000439203678693502</v>
+        <v>0.000443342732240052</v>
       </c>
     </row>
     <row r="65">
@@ -2486,10 +2486,10 @@
         <v>68</v>
       </c>
       <c r="C65" t="n">
-        <v>0.00225041923333027</v>
+        <v>0.00227428199182506</v>
       </c>
       <c r="D65" t="n">
-        <v>0.00105920119290938</v>
+        <v>0.00107021790321852</v>
       </c>
     </row>
     <row r="66">
@@ -2500,10 +2500,10 @@
         <v>79</v>
       </c>
       <c r="C66" t="n">
-        <v>0.00198338490524801</v>
+        <v>0.00200369287562616</v>
       </c>
       <c r="D66" t="n">
-        <v>0.00119184511494118</v>
+        <v>0.00120425109626506</v>
       </c>
     </row>
     <row r="67">
@@ -2514,10 +2514,10 @@
         <v>74</v>
       </c>
       <c r="C67" t="n">
-        <v>0.00158503534536518</v>
+        <v>0.001600256041685</v>
       </c>
       <c r="D67" t="n">
-        <v>0.000438099252088905</v>
+        <v>0.000442528587037495</v>
       </c>
     </row>
     <row r="68">
@@ -2528,10 +2528,10 @@
         <v>55</v>
       </c>
       <c r="C68" t="n">
-        <v>0.00129573703573949</v>
+        <v>0.00131085543723534</v>
       </c>
       <c r="D68" t="n">
-        <v>0.000222549817408171</v>
+        <v>0.000224937505409737</v>
       </c>
     </row>
     <row r="69">
@@ -2542,10 +2542,10 @@
         <v>75</v>
       </c>
       <c r="C69" t="n">
-        <v>0.00122325120571949</v>
+        <v>0.00123459932078208</v>
       </c>
       <c r="D69" t="n">
-        <v>0.000443761074703495</v>
+        <v>0.000447877851137056</v>
       </c>
     </row>
     <row r="70">
@@ -2556,10 +2556,10 @@
         <v>71</v>
       </c>
       <c r="C70" t="n">
-        <v>0.000737625058847254</v>
+        <v>0.000745702658952322</v>
       </c>
       <c r="D70" t="n">
-        <v>0.000120785549111243</v>
+        <v>0.00012122353094463</v>
       </c>
     </row>
     <row r="71">
@@ -2570,10 +2570,10 @@
         <v>80</v>
       </c>
       <c r="C71" t="n">
-        <v>0.000691940525290619</v>
+        <v>0.000699437172932251</v>
       </c>
       <c r="D71" t="n">
-        <v>0.000173346135716683</v>
+        <v>0.000175716182736292</v>
       </c>
     </row>
     <row r="72">
@@ -2584,10 +2584,10 @@
         <v>58</v>
       </c>
       <c r="C72" t="n">
-        <v>0.000628862951207552</v>
+        <v>0.000636335629408515</v>
       </c>
       <c r="D72" t="n">
-        <v>0.0000133052831442854</v>
+        <v>0.0000141747562044723</v>
       </c>
     </row>
     <row r="73">
@@ -2598,7 +2598,7 @@
         <v>73</v>
       </c>
       <c r="C73" t="n">
-        <v>0.000566808497155452</v>
+        <v>0.000574266697411671</v>
       </c>
       <c r="D73"/>
     </row>
@@ -2610,7 +2610,7 @@
         <v>70</v>
       </c>
       <c r="C74" t="n">
-        <v>0.000490452604409625</v>
+        <v>0.000495541292524534</v>
       </c>
       <c r="D74"/>
     </row>
@@ -2622,7 +2622,7 @@
         <v>81</v>
       </c>
       <c r="C75" t="n">
-        <v>0.000342811935593195</v>
+        <v>0.00034630647881205</v>
       </c>
       <c r="D75"/>
     </row>
@@ -2634,7 +2634,7 @@
         <v>72</v>
       </c>
       <c r="C76" t="n">
-        <v>0.000129535892616283</v>
+        <v>0.000131276352375242</v>
       </c>
       <c r="D76"/>
     </row>
